--- a/important_mails_2026-10-18.xlsx
+++ b/important_mails_2026-10-18.xlsx
@@ -1699,7 +1699,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>产品链接/合规类</t>
+          <t>法务/侵权类</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Sun, 11 Oct 2026 17:11:11 +0000</t>
+          <t>Sat, 17 Oct 2026 01:52:40 +0000</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1724,61 +1724,11 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Submit product safety documentation to reactivate listings</t>
+          <t>Återaktivera dina EU-produktposter – GPSR-efterlevnad krävs</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>96
- Submit product safety documentation to reactivate listings
- Hello Weihai EU,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 17 Oct 2026 01:52:40 +0000</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Återaktivera dina EU-produktposter – GPSR-efterlevnad krävs</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>96
  Återaktivera dina EU-produktposter – GPSR-efterlevnad krävs
@@ -1797,39 +1747,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Fri, 16 Oct 2026 18:05:00 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Réactivez vos mises en vente dans l’UE – Conformité au RSGP requise</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>96
  Réactivez vos mises en vente dans l’UE – Conformité au RSGP requise
@@ -1848,40 +1798,40 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Fri, 16 Oct 2026 01:16:51 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Reactiva tus listings en la UE: se requiere el cumplimiento del
  Reglamento relativo a la seguridad general de los productos</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>96
  Reactiva tus listings en la UE: se requiere el cumplimiento del Reglamento relativo a la seguridad general de los productos
@@ -1899,39 +1849,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Thu, 15 Oct 2026 20:26:08 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Activeer je EU-productvermeldingen opnieuw - VAPV-naleving vereist</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Activeer je EU-productvermeldingen opnieuw - VAPV-naleving vereist
@@ -1950,39 +1900,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Thu, 15 Oct 2026 14:24:32 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以避免商品被停售</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>96
  尊敬的 Weihai EU：
@@ -2021,39 +1971,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Thu, 15 Oct 2026 12:30:12 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Les réserves de frais pour le paiement REP : Nous payons en votre nom commencent le 7 octobre</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -2066,39 +2016,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Thu, 15 Oct 2026 09:15:20 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Umożliw ponowną aktywację ofert w UE – wymagana zgodność z rozporządzeniem w sprawie ogólnego bezpieczeństwa produktów</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>96
  Umożliw ponowną aktywację ofert w UE – wymagana zgodność z rozporządzeniem w sprawie ogólnego bezpieczeństwa produktów
@@ -2116,39 +2066,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Thu, 15 Oct 2026 03:49:43 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Återaktivera dina EU-produktposter – GPSR-efterlevnad krävs</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>96
  Återaktivera dina EU-produktposter – GPSR-efterlevnad krävs
@@ -2167,39 +2117,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Wed, 14 Oct 2026 22:40:40 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>96
  Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti
@@ -2218,39 +2168,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Wed, 14 Oct 2026 21:11:11 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Twoje konto spełnia już europejskie wymagania Amazon dotyczące rejestracji jako podatnik VAT</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>96
  Twoje konto spełnia już europejskie wymagania Amazon dotyczące rejestracji jako podatnik VAT
@@ -2276,39 +2226,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Wed, 14 Oct 2026 19:02:13 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Logística de Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Descarga las previsiones de demanda de tu cartera de Logística de Amazon</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>96
  Obtén previsiones semanales de tus productos en un solo fichero para planificar el inventario con confianza
@@ -2328,39 +2278,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Wed, 14 Oct 2026 17:50:21 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Réactivez vos mises en vente dans l’UE – Conformité au RSGP requise</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>96
  Réactivez vos mises en vente dans l’UE – Conformité au RSGP requise
@@ -2379,40 +2329,40 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Wed, 14 Oct 2026 04:11:58 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Reactiva tus listings en la UE: se requiere el cumplimiento del
  Reglamento relativo a la seguridad general de los productos</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>96
  Reactiva tus listings en la UE: se requiere el cumplimiento del Reglamento relativo a la seguridad general de los productos
@@ -2430,39 +2380,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Tue, 13 Oct 2026 09:09:18 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Umożliw ponowną aktywację ofert w UE – wymagana zgodność z rozporządzeniem w sprawie ogólnego bezpieczeństwa produktów</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>96
  Umożliw ponowną aktywację ofert w UE – wymagana zgodność z rozporządzeniem w sprawie ogólnego bezpieczeństwa produktów
@@ -2480,39 +2430,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Tue, 13 Oct 2026 04:11:35 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Återaktivera dina EU-produktposter – GPSR-efterlevnad krävs</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>96
  Återaktivera dina EU-produktposter – GPSR-efterlevnad krävs
@@ -2531,39 +2481,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Mon, 12 Oct 2026 23:54:30 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>96
  Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti
@@ -2582,39 +2532,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Mon, 12 Oct 2026 19:58:04 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Réactivez vos mises en vente dans l’UE – Conformité au RSGP requise</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>96
  Réactivez vos mises en vente dans l’UE – Conformité au RSGP requise
@@ -2633,39 +2583,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Mon, 12 Oct 2026 14:31:33 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Activeer je EU-productvermeldingen opnieuw - VAPV-naleving vereist</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Activeer je EU-productvermeldingen opnieuw - VAPV-naleving vereist
@@ -2684,39 +2634,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Mon, 12 Oct 2026 08:28:39 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -2732,40 +2682,40 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Mon, 12 Oct 2026 08:17:00 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Tu cuenta cumple ahora nuestros requisitos de registro a efectos
  fiscales en Europa</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>96
  Tu cuenta cumple ahora nuestros requisitos de registro a efectos fiscales en Europa
@@ -2791,39 +2741,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Mon, 12 Oct 2026 08:12:09 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Twoje konto spełnia już europejskie wymagania Amazon dotyczące rejestracji jako podatnik VAT</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>96
  Twoje konto spełnia już europejskie wymagania Amazon dotyczące rejestracji jako podatnik VAT
@@ -2849,40 +2799,40 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Mon, 12 Oct 2026 05:19:47 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -2898,39 +2848,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Mon, 12 Oct 2026 03:59:49 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Umożliw ponowną aktywację ofert w UE – wymagana zgodność z rozporządzeniem w sprawie ogólnego bezpieczeństwa produktów</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>96
  Umożliw ponowną aktywację ofert w UE – wymagana zgodność z rozporządzeniem w sprawie ogólnego bezpieczeństwa produktów
@@ -2948,141 +2898,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 11 Oct 2026 22:52:35 +0000</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>Återaktivera dina EU-produktposter – GPSR-efterlevnad krävs</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>96
- Återaktivera dina EU-produktposter – GPSR-efterlevnad krävs
- Hej Weihai EU!
- Vissa av dina produktposter har inaktiverats i våra butiker inom Europeiska unionen (EU) på grund av att information om överensstämmelse saknas. Den här åtgärden påverkar inte din kontostatus.
- Du hittar exempel på de produktposter som har inaktiverats längst ner i detta e-postmeddelande, och hela listan finns på sidan Kontostatus. Granska de berörda produktposterna och nästa steg för att uppfylla kraven i Förordningen om allmän produktsäkerhet (GPSR) nedan.
- Skicka in information om överensstämmelse
- Skicka in information om överensstämmelse
- Hur återaktiverar jag mina produktposter?
- Om du vill återaktivera dina produktposter behöver du ange den efterfrågade GPSR-informationen om överensstämmelse genom att följa anvisningarna nedan:
--
- Gå till sidan Kontostatus .
-- Välj Lägg till filter och markera Produktpost borttagen i kolumnen Filtrera efter vidtagen åtgärd.
-- Klicka på Skicka in bredvid den inaktiverade produktposten och följ instruktionerna.
-- Följ stegen på Dolda produktposter för att åtgärda eventuella kvarstående problem med produktposter. Befintliga problem förhindrar att produktposter åter</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 11 Oct 2026 18:40:34 +0000</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>96
- Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti
- Gentile Weihai EU,
- Alcune delle tue offerte sono state disattivate nei nostri negozi dell'Unione europea a causa della mancanza di informazioni relative alla conformità. Questa azione non avrà alcun impatto sullo stato del tuo account.
- Puoi trovare esempi delle tue offerte disattivate in fondo a questa e-mail e l'elenco completo nella pagina Stato dell'account. Rivedi le offerte interessate e i passaggi successivi per soddisfare i requisiti del Regolamento sulla sicurezza generale dei prodotti riportati di seguito.
- Inviare le informazioni sulla conformità
- Inviare le informazioni sulla conformità
- Come faccio a riattivare le mie offerte?
- Per riattivare le offerte, fornisci le informazioni richieste relative alla conformità al regolamento sulla sicurezza generale dei prodotti seguendo le istruzioni riportate di seguito:
--
- Vai alla pagina Stato dell'account .
-- Seleziona "Aggiungi filtri" e quindi "Offerta rimossa" nella colonna "Filtra per azione intrapresa".
-- Clicca su "Invia" accanto all'offerta disattivata e segui le istruzioni fornite.
-- Segui la procedura indi</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Sat, 17 Oct 2026 04:18:17 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-10-29</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -3103,39 +2951,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Sat, 17 Oct 2026 04:16:43 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-10-29</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -3158,39 +3006,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Sat, 17 Oct 2026 03:57:58 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -3214,40 +3062,40 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Thu, 15 Oct 2026 08:25:20 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>"seller-coaching-m@amazon.com" &lt;seller-coaching-m@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 13389411022] Optimize Your Next EU FBA Shipment Based on
  Inventory Health [A-AWD]</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 RE:[CASE 13389411022] Optimize Your Next EU FBA Shipment Based on Inventory Health [A-AWD]
@@ -3263,39 +3111,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Fri, 16 Oct 2026 02:02:21 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon Business &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Earn new Business Discount badge for always-on visibility</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>96
  New badge launches in two weeks - set your Business Price at least 5% below standard retail price to get started
@@ -3308,39 +3156,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Fri, 16 Oct 2026 09:43:53 +0800 (CST)</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号管理 &lt;fli.lin@nbtscn.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号情况跟进</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>尊敬的客户：
 您好！
@@ -3369,39 +3217,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Sun, 11 Oct 2026 09:31:41 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3417,39 +3265,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Sun, 11 Oct 2026 04:46:33 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3465,39 +3313,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Sat, 10 Oct 2026 14:54:13 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>"Amazon.ca" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>96
 Balance paid on your Amazon seller account
@@ -3518,39 +3366,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Sat, 10 Oct 2026 04:49:48 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3566,39 +3414,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Sat, 10 Oct 2026 00:57:30 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 Balance paid on your Amazon seller account
@@ -3616,39 +3464,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Fri, 9 Oct 2026 05:03:27 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3664,39 +3512,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Thu, 8 Oct 2026 16:07:57 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Amazon Multichannel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF
 As a valued Multichannel Fulfillment (MCF) managed customer, we are interested in learning about your program feedback including new features that may benefit your business. This may help us understand how we can better meet your business needs and continue to improve the customer experience.
@@ -3710,39 +3558,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Wed, 7 Oct 2026 05:17:16 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3758,39 +3606,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Tue, 6 Oct 2026 04:57:40 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3806,39 +3654,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Sat, 3 Oct 2026 17:10:17 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3859,39 +3707,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Sat, 3 Oct 2026 04:56:42 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3907,39 +3755,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Fri, 2 Oct 2026 04:48:02 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3955,39 +3803,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Fri, 2 Oct 2026 03:23:37 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Jl40SY3EId)</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -4007,39 +3855,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Tue, 29 Sep 2026 19:30:09 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (4sQeBGpWIe)</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -4059,39 +3907,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Tue, 29 Sep 2026 09:21:47 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4107,39 +3955,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Tue, 29 Sep 2026 05:14:04 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4155,39 +4003,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Mon, 28 Sep 2026 05:02:53 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4203,39 +4051,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Sun, 27 Sep 2026 23:20:30 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (cENUYoUvou)</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -4260,39 +4108,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Sun, 27 Sep 2026 04:48:00 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4308,39 +4156,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 16:39:11 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -4361,39 +4209,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Fri, 25 Sep 2026 04:50:51 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4409,39 +4257,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 04:54:38 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4457,39 +4305,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Wed, 23 Sep 2026 16:43:27 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (7iKN0D3u4y)</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -4509,39 +4357,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Wed, 23 Sep 2026 09:25:48 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4557,39 +4405,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Wed, 23 Sep 2026 05:04:18 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4605,39 +4453,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Tue, 22 Sep 2026 14:06:30 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Address variation policy violations</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>96
  Address variation policy violations
@@ -4653,39 +4501,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Tue, 22 Sep 2026 04:54:44 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4701,39 +4549,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Sun, 20 Sep 2026 14:23:10 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>96
 Balance paid on your Amazon seller account
@@ -4756,39 +4604,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Sat, 19 Sep 2026 04:50:14 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4804,39 +4652,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Sun, 20 Sep 2026 05:13:35 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>"Amazon.it" &lt;store-news@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Il tuo carrello chiama</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.it/gp/cart/view.html?ref_=cor
 Pista ferroviaria elettrica a cubi da 145 pezzi, set trenino 3D antigravità, gioco fai da te per costruire percorsi, giocattolo educativo STEM e idea regalo creativa per bambini da 3 a 8 anni
@@ -4857,39 +4705,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Sat, 10 Oct 2026 13:43:05 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>欧洲亚马逊 Payments &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>跨账户负余额调整</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4909,39 +4757,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Thu, 8 Oct 2026 12:48:14 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europa &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Ajuste de saldo negativo en tus cuentas de Vender en Amazon</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4965,39 +4813,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Wed, 7 Oct 2026 14:20:27 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Rettifica del saldo negativo nei tuoi account</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5021,39 +4869,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Wed, 7 Oct 2026 05:12:07 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>您的亚马逊卖家账户支付的余额</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>96
 您的亚马逊卖家账户支付的余额
@@ -5082,39 +4930,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Sun, 4 Oct 2026 13:38:25 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5134,39 +4982,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Fri, 2 Oct 2026 23:31:42 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -5186,39 +5034,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Thu, 1 Oct 2026 14:51:16 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -5234,39 +5082,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 13:36:40 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5286,39 +5134,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 13:33:11 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -5338,39 +5186,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 00:41:51 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -5390,39 +5238,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 12:37:44 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -5439,39 +5287,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Mon, 21 Sep 2026 17:07:48 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Ver el informe fiscal de China de abril a junio de 2026</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>96
  Presentamos tu declaración fiscal trimestral a la autoridad tributaria china. Ya puedes descargar la declaración para consultarla.
@@ -5487,39 +5335,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Mon, 21 Sep 2026 13:27:57 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Last chance to register for Amazon Accelerate 2026</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-11/7z5qvbd/6900257597/h/DNy5vrd2KmewvkDHEulcRelQOUFu36-wIzMILRKLzn4)
 [Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5qvbh/6900257597/h/DNy5vrd2KmewvkDHEulcRelQOUFu36-wIzMILRKLzn4)
@@ -5534,39 +5382,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Sun, 20 Sep 2026 14:07:50 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5586,39 +5434,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 11 Oct 2026 16:03:12 +0000</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 11 Oct 2026 17:11:11 +0000</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5636,39 +5484,89 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 11 Oct 2026 16:03:12 +0000</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Submit product safety documentation to reactivate listings
+ Hello Weihai EU,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Fri, 9 Oct 2026 07:35:36 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Submit missing VAT Registration Information</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  96
@@ -5695,39 +5593,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Thu, 8 Oct 2026 13:20:34 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5745,39 +5643,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Thu, 8 Oct 2026 12:56:57 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -5793,39 +5691,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Thu, 8 Oct 2026 11:25:17 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5843,39 +5741,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Wed, 7 Oct 2026 13:15:21 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5893,39 +5791,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Wed, 7 Oct 2026 11:16:06 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5943,39 +5841,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Wed, 7 Oct 2026 10:16:15 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5993,39 +5891,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Tue, 6 Oct 2026 13:03:41 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -6041,39 +5939,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Tue, 6 Oct 2026 10:13:01 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6091,39 +5989,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Mon, 5 Oct 2026 22:52:24 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6141,39 +6039,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Mon, 5 Oct 2026 14:42:52 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6191,39 +6089,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Sat, 3 Oct 2026 22:29:49 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6241,39 +6139,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Fri, 2 Oct 2026 19:40:11 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6291,39 +6189,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Wed, 30 Sep 2026 10:06:35 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -6341,39 +6239,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Tue, 29 Sep 2026 10:06:26 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -6391,39 +6289,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Tue, 29 Sep 2026 05:31:39 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>重要通知｜9月1日起，Pan-EU入库欧盟及直接发往法国的货件必须提供进口详情</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>未提供 MRN+EORI 将无法创建新货件，请在收货后 60 天内完成补全
 尊敬的 深圳市微海众信科技有限公司,
@@ -6451,39 +6349,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Mon, 28 Sep 2026 10:05:46 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hello Weihai CA,
@@ -6502,39 +6400,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Sun, 27 Sep 2026 10:05:10 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hello Weihai CA,
@@ -6553,39 +6451,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 01:10:33 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6603,39 +6501,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 01:07:50 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6653,39 +6551,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 14:57:06 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Zwrot kosztów zgodności z wymogami w zakresie opakowań w ramach ROP</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
  Dokończenie rejestracji w ramach ROP i uzyskanie częściowego zwrotu kosztów w Polsce
@@ -6702,39 +6600,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 14:07:32 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -6752,39 +6650,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 10:28:03 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Få ersättning för kostnader för överensstämmelse med EPR-förpackningar</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>96
  Slutför EPR-registreringen och få en del av kostnaderna återbetalda i Sverige
@@ -6802,39 +6700,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 10:08:29 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -6853,39 +6751,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 10:08:17 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -6904,39 +6802,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Tue, 22 Sep 2026 07:40:02 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>"pli-cn-seller-compliance@amazon.com" &lt;pli-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 22191892721] [立刻采取行动购买或更新商业责任险]</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 22191892721] [立刻采取行动购买或更新商业责任险]
@@ -6963,6 +6861,108 @@
 请您完成以下事项
 1.对照"商业责任险要求"和"计划政策变更"帮助页面核对您现有保单是否符合全部标准。
 2.查看"具有更严格</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 11 Oct 2026 22:52:35 +0000</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>Återaktivera dina EU-produktposter – GPSR-efterlevnad krävs</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Återaktivera dina EU-produktposter – GPSR-efterlevnad krävs
+ Hej Weihai EU!
+ Vissa av dina produktposter har inaktiverats i våra butiker inom Europeiska unionen (EU) på grund av att information om överensstämmelse saknas. Den här åtgärden påverkar inte din kontostatus.
+ Du hittar exempel på de produktposter som har inaktiverats längst ner i detta e-postmeddelande, och hela listan finns på sidan Kontostatus. Granska de berörda produktposterna och nästa steg för att uppfylla kraven i Förordningen om allmän produktsäkerhet (GPSR) nedan.
+ Skicka in information om överensstämmelse
+ Skicka in information om överensstämmelse
+ Hur återaktiverar jag mina produktposter?
+ Om du vill återaktivera dina produktposter behöver du ange den efterfrågade GPSR-informationen om överensstämmelse genom att följa anvisningarna nedan:
+-
+ Gå till sidan Kontostatus .
+- Välj Lägg till filter och markera Produktpost borttagen i kolumnen Filtrera efter vidtagen åtgärd.
+- Klicka på Skicka in bredvid den inaktiverade produktposten och följ instruktionerna.
+- Följ stegen på Dolda produktposter för att åtgärda eventuella kvarstående problem med produktposter. Befintliga problem förhindrar att produktposter åter</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 11 Oct 2026 18:40:34 +0000</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti
+ Gentile Weihai EU,
+ Alcune delle tue offerte sono state disattivate nei nostri negozi dell'Unione europea a causa della mancanza di informazioni relative alla conformità. Questa azione non avrà alcun impatto sullo stato del tuo account.
+ Puoi trovare esempi delle tue offerte disattivate in fondo a questa e-mail e l'elenco completo nella pagina Stato dell'account. Rivedi le offerte interessate e i passaggi successivi per soddisfare i requisiti del Regolamento sulla sicurezza generale dei prodotti riportati di seguito.
+ Inviare le informazioni sulla conformità
+ Inviare le informazioni sulla conformità
+ Come faccio a riattivare le mie offerte?
+ Per riattivare le offerte, fornisci le informazioni richieste relative alla conformità al regolamento sulla sicurezza generale dei prodotti seguendo le istruzioni riportate di seguito:
+-
+ Vai alla pagina Stato dell'account .
+- Seleziona "Aggiungi filtri" e quindi "Offerta rimossa" nella colonna "Filtra per azione intrapresa".
+- Clicca su "Invia" accanto all'offerta disattivata e segui le istruzioni fornite.
+- Segui la procedura indi</t>
         </is>
       </c>
     </row>
